--- a/riparazionitool.xlsx
+++ b/riparazionitool.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -586,86 +586,1462 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TLS-147</t>
+          <t>TLS-118</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kit 4 vie fibre ottiche per prove</t>
+          <t>Simulatore prove RIA su banco rack</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sostituito componente danneggiato, ripristinata funzionalita'.</t>
+          <t>Connettore di prova danneggiato</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Non specificato (dato migrato)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
+          <t>Alimentatore switching</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Davide Colombo</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TLS-133</t>
+          <t>S-2201</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Cavo di collegamento MVB tester dispositivo</t>
+          <t>Connettore prova di rigidità dielettrica</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sostituito componente danneggiato, ripristinata funzionalita'.</t>
+          <t>Fallimento autotest all'accensione</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Non specificato (dato migrato)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>Scheda di interfaccia USB</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DTR-041</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Dispositivo uomo morto test 72VCC</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Usura cavo di collegamento</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Connettore BNC</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Deriva della calibrazione oltre tolleranza</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TLS-118</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Simulatore prove RIA su banco rack</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Errore di comunicazione con PC di controllo</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Modulo di controllo</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>TLS-147</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Kit 4 vie fibre ottiche per prove</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Sostituito componente danneggiato, ripristinata funzionalita'.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Non specificato (dato migrato)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DTR0001</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>PROLUNGA DIS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Guasto elettrico su alimentazione interna</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Ventola di raffreddamento</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Simone Ricci</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>S-2201</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Connettore prova di rigidità dielettrica</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Surriscaldamento durante ciclo di prova prolungato</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Sensore di temperatura</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Chiara Ferrari</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>TLS-102</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Rack collaudo scheda DSP VME SMD</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Usura meccanica su componente di prova</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ventola di raffreddamento</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Simone Ricci</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DTR-027</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Scheda regolatore di trazione IC2500</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Surriscaldamento durante ciclo di prova prolungato</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Scheda di interfaccia USB</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Davide Colombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>TLS-147</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Kit 4 vie fibre ottiche per prove</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Usura meccanica su componente di prova</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>TLS-147</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Kit 4 vie fibre ottiche per prove</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Surriscaldamento durante ciclo di prova prolungato</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Modulo di controllo</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Simone Ricci</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>TLS-133</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di collegamento MVB tester dispositivo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Fallimento autotest all'accensione</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Supporto meccanico</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Marco Bianchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>TLS-102</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Rack collaudo scheda DSP VME SMD</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Guasto elettrico su alimentazione interna</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Sonda di misura</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Luca Marino</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DTR0001</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>PROLUNGA DIS</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Deriva della calibrazione oltre tolleranza</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Ventola di raffreddamento</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Davide Colombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>TLS-147</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Kit 4 vie fibre ottiche per prove</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Usura cavo di collegamento</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DTR-014</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Scheda regolatore di trazione IC2500</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Errore di comunicazione con PC di controllo</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Ventola di raffreddamento</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>TLS-118</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Simulatore prove RIA su banco rack</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Sensore di misura fuori specifica</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Supporto meccanico</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Davide Colombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>S-2214</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Scheda CPU moduli I/O compatta</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sensore di misura fuori specifica</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>TLS-133</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di collegamento MVB tester dispositivo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Sostituito componente danneggiato, ripristinata funzionalita'.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Non specificato (dato migrato)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>DTR-041</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Dispositivo uomo morto test 72VCC</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Usura meccanica su componente di prova</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Sensore di temperatura</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Davide Colombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>S-2214</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Scheda CPU moduli I/O compatta</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Guasto elettrico su alimentazione interna</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Modulo di controllo</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Chiara Ferrari</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>S-2214</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Scheda CPU moduli I/O compatta</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Usura meccanica su componente di prova</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Supporto meccanico</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>S-2214</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Scheda CPU moduli I/O compatta</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sostituito componente danneggiato, ripristinata funzionalita'.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Non specificato (dato migrato)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Guasto elettrico su alimentazione interna</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Supporto meccanico</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Davide Colombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Connettore di prova danneggiato</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Supporto meccanico</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>TLS-118</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Simulatore prove RIA su banco rack</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Rottura meccanica supporto attrezzatura</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Alimentatore switching</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Luca Marino</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>TLS-147</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Kit 4 vie fibre ottiche per prove</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Usura meccanica su componente di prova</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Connettore BNC</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Luca Marino</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>S-2201</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Connettore prova di rigidità dielettrica</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Surriscaldamento durante ciclo di prova prolungato</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>S-2214</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Scheda CPU moduli I/O compatta</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Connettore di prova danneggiato</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Connettore BNC</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Simone Ricci</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Connettore di prova danneggiato</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Scheda di interfaccia USB</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Chiara Ferrari</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Rottura meccanica supporto attrezzatura</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Scheda di interfaccia USB</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>TLS-147</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Kit 4 vie fibre ottiche per prove</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Deriva della calibrazione oltre tolleranza</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>TLS-102</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Rack collaudo scheda DSP VME SMD</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Errore di comunicazione con PC di controllo</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Alimentatore switching</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>TLS-118</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Simulatore prove RIA su banco rack</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Deriva della calibrazione oltre tolleranza</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Sonda di misura</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Fallimento autotest all'accensione</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Alimentatore switching</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Giulia Moretti</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Guasto elettrico su alimentazione interna</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Supporto meccanico</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Simone Ricci</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>DTR0001</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>PROLUNGA DIS</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Usura meccanica su componente di prova</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Ventola di raffreddamento</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Connettore di prova danneggiato</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Sonda di misura</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>DTR-027</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Scheda regolatore di trazione IC2500</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Errore di comunicazione con PC di controllo</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Connettore BNC</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Chiara Ferrari</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>S-2201</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Connettore prova di rigidità dielettrica</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Sensore di misura fuori specifica</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Connettore BNC</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Davide Colombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>TLS-133</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di collegamento MVB tester dispositivo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Rottura meccanica supporto attrezzatura</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Ventola di raffreddamento</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Chiara Ferrari</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>TLS-147</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Kit 4 vie fibre ottiche per prove</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Deriva della calibrazione oltre tolleranza</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Supporto meccanico</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>TLS-118</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Simulatore prove RIA su banco rack</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Usura meccanica su componente di prova</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Fusibile interno</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Federica Galli</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TLS-118</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Simulatore prove RIA su banco rack</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Surriscaldamento durante ciclo di prova prolungato</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Cavo di alimentazione</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>S-2255</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Scheda encoder comparatore velocità</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Deriva della calibrazione oltre tolleranza</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Sonda di misura</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Marco Bianchi</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
